--- a/property_management_forms/049_junior_on_site_property_manager_application_form--property_management_forms.xlsx
+++ b/property_management_forms/049_junior_on_site_property_manager_application_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'6-12_months'}</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '6-12 months'}</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'2-3_years'}</t>
+          <t>2-3_years</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '2-3 years'}</t>
+          <t>2-3 years</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'3-4_years'}</t>
+          <t>3-4_years</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '3-4 years'}</t>
+          <t>3-4 years</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'4-5_years'}</t>
+          <t>4-5_years</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '4-5 years'}</t>
+          <t>4-5 years</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'on-site_property_manager'}</t>
+          <t>on-site_property_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'On-site Property Manager'}</t>
+          <t>On-site Property Manager</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'assistant_property_manager'}</t>
+          <t>assistant_property_manager</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Assistant Property Manager'}</t>
+          <t>Assistant Property Manager</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'property_manager'}</t>
+          <t>property_manager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Property Manager'}</t>
+          <t>Property Manager</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'off-site'}</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Off-site'}</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
